--- a/output/pdf_financials_xlsx/ORCL.xlsx
+++ b/output/pdf_financials_xlsx/ORCL.xlsx
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.128019</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.294541</v>
       </c>
     </row>
     <row r="93">
@@ -3870,7 +3870,11 @@
           <t>Reserves (note 12)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4550,7 +4554,11 @@
           <t>Reserves (note 14)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ORCL.xlsx
+++ b/output/pdf_financials_xlsx/ORCL.xlsx
@@ -645,10 +645,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.142934</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.641755</v>
       </c>
     </row>
     <row r="13">
@@ -936,25 +936,17 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>77.714286</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>80.383489</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>102.788563</v>
       </c>
     </row>
     <row r="27">
@@ -970,10 +962,10 @@
         <v>-5.809393</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.599991</v>
+        <v>-5.742925</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.151281</v>
+        <v>-7.793036</v>
       </c>
     </row>
     <row r="28">
@@ -1008,10 +1000,10 @@
         <v>-5.809393</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.599991</v>
+        <v>-5.742925</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.151281</v>
+        <v>-7.793036</v>
       </c>
     </row>
     <row r="30">
@@ -1104,13 +1096,13 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.371018</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.727844</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.22448</v>
       </c>
     </row>
     <row r="35">
@@ -1142,13 +1134,13 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.371018</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.727844</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.22448</v>
       </c>
     </row>
     <row r="37">
@@ -1370,13 +1362,13 @@
         <v>1e-06</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.740764</v>
+        <v>0.369746</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.753484</v>
+        <v>0.02564</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.685577</v>
+        <v>0.461097</v>
       </c>
     </row>
     <row r="49">
@@ -3140,7 +3132,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6886,7 +6878,11 @@
           <t>Prepaid expenses and reclamation deposits</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -8640,7 +8636,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9342,7 +9338,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10514,7 +10510,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">

--- a/output/pdf_financials_xlsx/ORCL.xlsx
+++ b/output/pdf_financials_xlsx/ORCL.xlsx
@@ -547,13 +547,13 @@
         <v>0.09986200000000001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.444464</v>
+        <v>1.61438</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.557181</v>
+        <v>0.6473139999999999</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.320998</v>
+        <v>0.368998</v>
       </c>
     </row>
     <row r="8">
@@ -604,13 +604,13 @@
         <v>0.104862</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.765666</v>
+        <v>2.935582</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.48604</v>
+        <v>1.576173</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.798154</v>
+        <v>0.846154</v>
       </c>
     </row>
     <row r="11">
@@ -6156,7 +6156,11 @@
           <t>Proceeds from share issuance (note 12)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -7274,7 +7278,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -8288,7 +8296,11 @@
           <t>Directors’ fee (note 14)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -9968,7 +9980,11 @@
           <t>Directors’ fee (note 16)</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
